--- a/artfynd/S 2501-2026 artfynd.xlsx
+++ b/artfynd/S 2501-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136583149</v>
       </c>
       <c r="B4" t="n">
-        <v>92541</v>
+        <v>92543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2501-2026 artfynd.xlsx
+++ b/artfynd/S 2501-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136583149</v>
       </c>
       <c r="B4" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2501-2026 artfynd.xlsx
+++ b/artfynd/S 2501-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136583149</v>
       </c>
       <c r="B4" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2501-2026 artfynd.xlsx
+++ b/artfynd/S 2501-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136583149</v>
       </c>
       <c r="B4" t="n">
-        <v>92547</v>
+        <v>92548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2501-2026 artfynd.xlsx
+++ b/artfynd/S 2501-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136583149</v>
       </c>
       <c r="B4" t="n">
-        <v>92548</v>
+        <v>92554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2501-2026 artfynd.xlsx
+++ b/artfynd/S 2501-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136583149</v>
       </c>
       <c r="B4" t="n">
-        <v>92554</v>
+        <v>92558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2501-2026 artfynd.xlsx
+++ b/artfynd/S 2501-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136583149</v>
       </c>
       <c r="B4" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
